--- a/input.xlsx
+++ b/input.xlsx
@@ -4,7 +4,6 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Steps" sheetId="1" r:id="rId1"/>
-    <sheet name="Config" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -402,7 +401,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>step</v>
+        <v>Step</v>
       </c>
     </row>
     <row r="2">
@@ -417,12 +416,12 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Enter username demo.user@example.com</v>
+        <v>Enter username</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Enter password Pass@12345</v>
+        <v>Enter password</v>
       </c>
     </row>
     <row r="6">
@@ -525,55 +524,4 @@
     <ignoredError numberStoredAsText="1" sqref="A1:A24"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>key</v>
-      </c>
-      <c r="B1" t="str">
-        <v>value</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>appId</v>
-      </c>
-      <c r="B2" t="str">
-        <v>smartparity-demo-app</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>appCredentials</v>
-      </c>
-      <c r="B3" t="str">
-        <v>demo-secure-token-123</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>preMigrationUrl</v>
-      </c>
-      <c r="B4" t="str">
-        <v>http://localhost:3000/</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>postMigrationUrl</v>
-      </c>
-      <c r="B5" t="str">
-        <v>http://localhost:3001/</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B5"/>
-  </ignoredErrors>
-</worksheet>
 </file>